--- a/parte2/tabela_tempo.xlsx
+++ b/parte2/tabela_tempo.xlsx
@@ -124,21 +124,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="&quot;Google Sans Text&quot;"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9900FF"/>
+        <bgColor rgb="FF9900FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+        <bgColor rgb="FFEFEFEF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -147,29 +161,32 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf quotePrefix="1" borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -394,7 +411,7 @@
     <col customWidth="1" min="11" max="11" width="87.88"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,7 +447,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2">
@@ -460,47 +477,47 @@
       <c r="J2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="E3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="2">
@@ -530,39 +547,39 @@
       <c r="J4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="E5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -570,7 +587,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="2">
@@ -600,7 +617,7 @@
       <c r="J6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -619,40 +636,40 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="2">
         <v>4.0</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="6">
         <v>0.7</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <f t="shared" ref="D10:D11" si="1">B10*C10</f>
         <v>2.8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="2">
         <v>3.0</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="6">
         <v>0.3</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <f>SUM(D10:D11)</f>
         <v>3.7</v>
       </c>
